--- a/docs/column/rosai-hokenryoritsu/rosai-table.xlsx
+++ b/docs/column/rosai-hokenryoritsu/rosai-table.xlsx
@@ -5,8 +5,8 @@
     <sheet name="一覧表" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">一覧表!$A$1:$D$59</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">一覧表!$6:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">一覧表!$A$1:$D$60</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">一覧表!$7:$7</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -73,7 +73,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D60"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
@@ -116,61 +116,48 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">令和8年度の据え置きの案内：https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/koyou_roudou/roudoukijun/rousai/rousaihoken06/rousai_hokenritsu_kaitei.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">分類</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">事業の種類</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">基準率（/1,000）</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">出典</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">林業</t>
-        </is>
-      </c>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">林業</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="D7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mhlw.go.jp/content/rousaihokenritu_r05.pdf</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">漁業</t>
+          <t xml:space="preserve">林業</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">海面漁業（定置網漁業又は海面魚類養殖業を除く。）</t>
+          <t xml:space="preserve">林業</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
@@ -186,51 +173,51 @@
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">海面漁業（定置網漁業又は海面魚類養殖業を除く。）</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mhlw.go.jp/content/rousaihokenritu_r05.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">漁業</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">定置網漁業又は海面魚類養殖業</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C10" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="D9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mhlw.go.jp/content/rousaihokenritu_r05.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="0" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mhlw.go.jp/content/rousaihokenritu_r05.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">鉱業</t>
         </is>
       </c>
-      <c r="B10" s="0" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">金属鉱業、非金属鉱業（石灰石鉱業又はドロマイト鉱業を除く。）又は石炭鉱業</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C11" s="2" t="n">
         <v>88</v>
-      </c>
-      <c r="D10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mhlw.go.jp/content/rousaihokenritu_r05.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">鉱業</t>
-        </is>
-      </c>
-      <c r="B11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">石灰石鉱業又はドロマイト鉱業</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>13</v>
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
@@ -246,11 +233,11 @@
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">原油又は天然ガス鉱業</t>
+          <t xml:space="preserve">石灰石鉱業又はドロマイト鉱業</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
@@ -266,11 +253,11 @@
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">採石業</t>
+          <t xml:space="preserve">原油又は天然ガス鉱業</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>37</v>
+        <v>2.5</v>
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
@@ -286,11 +273,11 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他の鉱業</t>
+          <t xml:space="preserve">採石業</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
@@ -301,16 +288,16 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">建設事業</t>
+          <t xml:space="preserve">鉱業</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">水力発電施設、ずい道等新設事業</t>
+          <t xml:space="preserve">その他の鉱業</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
@@ -326,11 +313,11 @@
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">道路新設事業</t>
+          <t xml:space="preserve">水力発電施設、ずい道等新設事業</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
@@ -346,11 +333,11 @@
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">舗装工事業</t>
+          <t xml:space="preserve">道路新設事業</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
@@ -366,7 +353,7 @@
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">鉄道又は軌道新設事業</t>
+          <t xml:space="preserve">舗装工事業</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -386,11 +373,11 @@
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">建築事業（既設建築物設備工事業を除く。）</t>
+          <t xml:space="preserve">鉄道又は軌道新設事業</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="D19" s="0" t="inlineStr">
         <is>
@@ -406,11 +393,11 @@
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">既設建築物設備工事業</t>
+          <t xml:space="preserve">建築事業（既設建築物設備工事業を除く。）</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
@@ -426,11 +413,11 @@
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">機械装置の組立て又は据付けの事業</t>
+          <t xml:space="preserve">既設建築物設備工事業</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
@@ -446,11 +433,11 @@
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他の建設事業</t>
+          <t xml:space="preserve">機械装置の組立て又は据付けの事業</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
@@ -461,16 +448,16 @@
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">製造業</t>
+          <t xml:space="preserve">建設事業</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">食料品製造業</t>
+          <t xml:space="preserve">その他の建設事業</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>5.5</v>
+        <v>15</v>
       </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
@@ -486,11 +473,11 @@
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">繊維工業又は繊維製品製造業</t>
+          <t xml:space="preserve">食料品製造業</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
@@ -506,11 +493,11 @@
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">木材又は木製品製造業</t>
+          <t xml:space="preserve">繊維工業又は繊維製品製造業</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D25" s="0" t="inlineStr">
         <is>
@@ -526,11 +513,11 @@
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">パルプ又は紙製造業</t>
+          <t xml:space="preserve">木材又は木製品製造業</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D26" s="0" t="inlineStr">
         <is>
@@ -546,11 +533,11 @@
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">印刷又は製本業</t>
+          <t xml:space="preserve">パルプ又は紙製造業</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
@@ -566,11 +553,11 @@
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">化学工業</t>
+          <t xml:space="preserve">印刷又は製本業</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
@@ -586,11 +573,11 @@
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ガラス又はセメント製造業</t>
+          <t xml:space="preserve">化学工業</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
@@ -606,11 +593,11 @@
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">コンクリート製造業</t>
+          <t xml:space="preserve">ガラス又はセメント製造業</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D30" s="0" t="inlineStr">
         <is>
@@ -626,11 +613,11 @@
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">陶磁器製品製造業</t>
+          <t xml:space="preserve">コンクリート製造業</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D31" s="0" t="inlineStr">
         <is>
@@ -646,11 +633,11 @@
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他の窯業又は土石製品製造業</t>
+          <t xml:space="preserve">陶磁器製品製造業</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D32" s="0" t="inlineStr">
         <is>
@@ -666,11 +653,11 @@
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">金属精錬業（非鉄金属精錬業を除く。）</t>
+          <t xml:space="preserve">その他の窯業又は土石製品製造業</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>6.5</v>
+        <v>23</v>
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
@@ -686,11 +673,11 @@
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">非鉄金属精錬業</t>
+          <t xml:space="preserve">金属精錬業（非鉄金属精錬業を除く。）</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="D34" s="0" t="inlineStr">
         <is>
@@ -706,11 +693,11 @@
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">金属材料品製造業（鋳物業を除く。）</t>
+          <t xml:space="preserve">非鉄金属精錬業</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
@@ -726,51 +713,51 @@
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">金属材料品製造業（鋳物業を除く。）</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mhlw.go.jp/content/rousaihokenritu_r05.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">製造業</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">鋳物業</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
+      <c r="C37" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D36" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mhlw.go.jp/content/rousaihokenritu_r05.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="42" customHeight="1">
-      <c r="A37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">製造業</t>
-        </is>
-      </c>
-      <c r="B37" s="0" t="inlineStr">
+      <c r="D37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mhlw.go.jp/content/rousaihokenritu_r05.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">製造業</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">金属製品製造業又は金属加工業（洋食器、刃物、手工具又は一般金物製造業及びめつき業を除く。）</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
+      <c r="C38" s="2" t="n">
         <v>9</v>
-      </c>
-      <c r="D37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mhlw.go.jp/content/rousaihokenritu_r05.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">製造業</t>
-        </is>
-      </c>
-      <c r="B38" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">洋食器、刃物、手工具又は一般金物製造業（めつき業を除く。）</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>6.5</v>
       </c>
       <c r="D38" s="0" t="inlineStr">
         <is>
@@ -786,7 +773,7 @@
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">めつき業</t>
+          <t xml:space="preserve">洋食器、刃物、手工具又は一般金物製造業（めつき業を除く。）</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -798,7 +785,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="42" customHeight="1">
+    <row r="40" ht="30" customHeight="1">
       <c r="A40" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">製造業</t>
@@ -806,31 +793,31 @@
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">めつき業</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mhlw.go.jp/content/rousaihokenritu_r05.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">製造業</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">機械器具製造業（電気機械器具製造業、輸送用機械器具製造業、船舶製造又は修理業及び計量器、光学機械、時計等製造業を除く。）</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n">
+      <c r="C41" s="2" t="n">
         <v>5</v>
-      </c>
-      <c r="D40" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mhlw.go.jp/content/rousaihokenritu_r05.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">製造業</t>
-        </is>
-      </c>
-      <c r="B41" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">電気機械器具製造業</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>3</v>
       </c>
       <c r="D41" s="0" t="inlineStr">
         <is>
@@ -846,11 +833,11 @@
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">輸送用機械器具製造業（船舶製造又は修理業を除く。）</t>
+          <t xml:space="preserve">電気機械器具製造業</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D42" s="0" t="inlineStr">
         <is>
@@ -866,11 +853,11 @@
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">船舶製造又は修理業</t>
+          <t xml:space="preserve">輸送用機械器具製造業（船舶製造又は修理業を除く。）</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D43" s="0" t="inlineStr">
         <is>
@@ -886,11 +873,11 @@
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">計量器、光学機械、時計等製造業（電気機械器具製造業を除く。）</t>
+          <t xml:space="preserve">船舶製造又は修理業</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>2.5</v>
+        <v>23</v>
       </c>
       <c r="D44" s="0" t="inlineStr">
         <is>
@@ -906,11 +893,11 @@
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">貴金属製品、装身具、皮革製品等製造業</t>
+          <t xml:space="preserve">計量器、光学機械、時計等製造業（電気機械器具製造業を除く。）</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="D45" s="0" t="inlineStr">
         <is>
@@ -926,11 +913,11 @@
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他の製造業</t>
+          <t xml:space="preserve">貴金属製品、装身具、皮革製品等製造業</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="D46" s="0" t="inlineStr">
         <is>
@@ -941,16 +928,16 @@
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">運輸業</t>
+          <t xml:space="preserve">製造業</t>
         </is>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">交通運輸事業</t>
+          <t xml:space="preserve">その他の製造業</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D47" s="0" t="inlineStr">
         <is>
@@ -966,11 +953,11 @@
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">貨物取扱事業（港湾貨物取扱事業及び港湾荷役業を除く。）</t>
+          <t xml:space="preserve">交通運輸事業</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="D48" s="0" t="inlineStr">
         <is>
@@ -986,11 +973,11 @@
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">港湾貨物取扱事業（港湾荷役業を除く。）</t>
+          <t xml:space="preserve">貨物取扱事業（港湾貨物取扱事業及び港湾荷役業を除く。）</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="D49" s="0" t="inlineStr">
         <is>
@@ -1006,11 +993,11 @@
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">港湾荷役業</t>
+          <t xml:space="preserve">港湾貨物取扱事業（港湾荷役業を除く。）</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D50" s="0" t="inlineStr">
         <is>
@@ -1021,16 +1008,16 @@
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">電気、ガス、水道又は熱供給の事業</t>
+          <t xml:space="preserve">運輸業</t>
         </is>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">電気、ガス、水道又は熱供給の事業</t>
+          <t xml:space="preserve">港湾荷役業</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D51" s="0" t="inlineStr">
         <is>
@@ -1041,16 +1028,16 @@
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">その他の事業</t>
+          <t xml:space="preserve">電気、ガス、水道又は熱供給の事業</t>
         </is>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">農業又は海面漁業以外の漁業</t>
+          <t xml:space="preserve">電気、ガス、水道又は熱供給の事業</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D52" s="0" t="inlineStr">
         <is>
@@ -1066,7 +1053,7 @@
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">清掃、火葬又はと畜の事業</t>
+          <t xml:space="preserve">農業又は海面漁業以外の漁業</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
@@ -1086,11 +1073,11 @@
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルメンテナンス業</t>
+          <t xml:space="preserve">清掃、火葬又はと畜の事業</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D54" s="0" t="inlineStr">
         <is>
@@ -1106,11 +1093,11 @@
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">倉庫業、警備業、消毒又は害虫駆除の事業又はゴルフ場の事業</t>
+          <t xml:space="preserve">ビルメンテナンス業</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="D55" s="0" t="inlineStr">
         <is>
@@ -1126,11 +1113,11 @@
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">通信業、放送業、新聞業又は出版業</t>
+          <t xml:space="preserve">倉庫業、警備業、消毒又は害虫駆除の事業又はゴルフ場の事業</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="D56" s="0" t="inlineStr">
         <is>
@@ -1146,11 +1133,11 @@
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">卸売業・小売業、飲食店又は宿泊業</t>
+          <t xml:space="preserve">通信業、放送業、新聞業又は出版業</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D57" s="0" t="inlineStr">
         <is>
@@ -1166,11 +1153,11 @@
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">金融業、保険業又は不動産業</t>
+          <t xml:space="preserve">卸売業・小売業、飲食店又は宿泊業</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D58" s="0" t="inlineStr">
         <is>
@@ -1186,81 +1173,104 @@
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">金融業、保険業又は不動産業</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mhlw.go.jp/content/rousaihokenritu_r05.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">その他の事業</t>
+        </is>
+      </c>
+      <c r="B60" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">その他の各種事業</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
+      <c r="C60" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D59" s="0" t="inlineStr">
+      <c r="D60" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mhlw.go.jp/content/rousaihokenritu_r05.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:D59"/>
-  <mergeCells count="5">
+  <autoFilter ref="A7:D60"/>
+  <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D7" r:id="rId7"/>
-    <hyperlink ref="D8" r:id="rId8"/>
-    <hyperlink ref="D9" r:id="rId9"/>
-    <hyperlink ref="D10" r:id="rId10"/>
-    <hyperlink ref="D11" r:id="rId11"/>
-    <hyperlink ref="D12" r:id="rId12"/>
-    <hyperlink ref="D13" r:id="rId13"/>
-    <hyperlink ref="D14" r:id="rId14"/>
-    <hyperlink ref="D15" r:id="rId15"/>
-    <hyperlink ref="D16" r:id="rId16"/>
-    <hyperlink ref="D17" r:id="rId17"/>
-    <hyperlink ref="D18" r:id="rId18"/>
-    <hyperlink ref="D19" r:id="rId19"/>
-    <hyperlink ref="D20" r:id="rId20"/>
-    <hyperlink ref="D21" r:id="rId21"/>
-    <hyperlink ref="D22" r:id="rId22"/>
-    <hyperlink ref="D23" r:id="rId23"/>
-    <hyperlink ref="D24" r:id="rId24"/>
-    <hyperlink ref="D25" r:id="rId25"/>
-    <hyperlink ref="D26" r:id="rId26"/>
-    <hyperlink ref="D27" r:id="rId27"/>
-    <hyperlink ref="D28" r:id="rId28"/>
-    <hyperlink ref="D29" r:id="rId29"/>
-    <hyperlink ref="D30" r:id="rId30"/>
-    <hyperlink ref="D31" r:id="rId31"/>
-    <hyperlink ref="D32" r:id="rId32"/>
-    <hyperlink ref="D33" r:id="rId33"/>
-    <hyperlink ref="D34" r:id="rId34"/>
-    <hyperlink ref="D35" r:id="rId35"/>
-    <hyperlink ref="D36" r:id="rId36"/>
-    <hyperlink ref="D37" r:id="rId37"/>
-    <hyperlink ref="D38" r:id="rId38"/>
-    <hyperlink ref="D39" r:id="rId39"/>
-    <hyperlink ref="D40" r:id="rId40"/>
-    <hyperlink ref="D41" r:id="rId41"/>
-    <hyperlink ref="D42" r:id="rId42"/>
-    <hyperlink ref="D43" r:id="rId43"/>
-    <hyperlink ref="D44" r:id="rId44"/>
-    <hyperlink ref="D45" r:id="rId45"/>
-    <hyperlink ref="D46" r:id="rId46"/>
-    <hyperlink ref="D47" r:id="rId47"/>
-    <hyperlink ref="D48" r:id="rId48"/>
-    <hyperlink ref="D49" r:id="rId49"/>
-    <hyperlink ref="D50" r:id="rId50"/>
-    <hyperlink ref="D51" r:id="rId51"/>
-    <hyperlink ref="D52" r:id="rId52"/>
-    <hyperlink ref="D53" r:id="rId53"/>
-    <hyperlink ref="D54" r:id="rId54"/>
-    <hyperlink ref="D55" r:id="rId55"/>
-    <hyperlink ref="D56" r:id="rId56"/>
-    <hyperlink ref="D57" r:id="rId57"/>
-    <hyperlink ref="D58" r:id="rId58"/>
-    <hyperlink ref="D59" r:id="rId59"/>
+    <hyperlink ref="A4" r:id="rId1"/>
+    <hyperlink ref="A6" r:id="rId2"/>
+    <hyperlink ref="D8" r:id="rId3"/>
+    <hyperlink ref="D9" r:id="rId4"/>
+    <hyperlink ref="D10" r:id="rId5"/>
+    <hyperlink ref="D11" r:id="rId6"/>
+    <hyperlink ref="D12" r:id="rId7"/>
+    <hyperlink ref="D13" r:id="rId8"/>
+    <hyperlink ref="D14" r:id="rId9"/>
+    <hyperlink ref="D15" r:id="rId10"/>
+    <hyperlink ref="D16" r:id="rId11"/>
+    <hyperlink ref="D17" r:id="rId12"/>
+    <hyperlink ref="D18" r:id="rId13"/>
+    <hyperlink ref="D19" r:id="rId14"/>
+    <hyperlink ref="D20" r:id="rId15"/>
+    <hyperlink ref="D21" r:id="rId16"/>
+    <hyperlink ref="D22" r:id="rId17"/>
+    <hyperlink ref="D23" r:id="rId18"/>
+    <hyperlink ref="D24" r:id="rId19"/>
+    <hyperlink ref="D25" r:id="rId20"/>
+    <hyperlink ref="D26" r:id="rId21"/>
+    <hyperlink ref="D27" r:id="rId22"/>
+    <hyperlink ref="D28" r:id="rId23"/>
+    <hyperlink ref="D29" r:id="rId24"/>
+    <hyperlink ref="D30" r:id="rId25"/>
+    <hyperlink ref="D31" r:id="rId26"/>
+    <hyperlink ref="D32" r:id="rId27"/>
+    <hyperlink ref="D33" r:id="rId28"/>
+    <hyperlink ref="D34" r:id="rId29"/>
+    <hyperlink ref="D35" r:id="rId30"/>
+    <hyperlink ref="D36" r:id="rId31"/>
+    <hyperlink ref="D37" r:id="rId32"/>
+    <hyperlink ref="D38" r:id="rId33"/>
+    <hyperlink ref="D39" r:id="rId34"/>
+    <hyperlink ref="D40" r:id="rId35"/>
+    <hyperlink ref="D41" r:id="rId36"/>
+    <hyperlink ref="D42" r:id="rId37"/>
+    <hyperlink ref="D43" r:id="rId38"/>
+    <hyperlink ref="D44" r:id="rId39"/>
+    <hyperlink ref="D45" r:id="rId40"/>
+    <hyperlink ref="D46" r:id="rId41"/>
+    <hyperlink ref="D47" r:id="rId42"/>
+    <hyperlink ref="D48" r:id="rId43"/>
+    <hyperlink ref="D49" r:id="rId44"/>
+    <hyperlink ref="D50" r:id="rId45"/>
+    <hyperlink ref="D51" r:id="rId46"/>
+    <hyperlink ref="D52" r:id="rId47"/>
+    <hyperlink ref="D53" r:id="rId48"/>
+    <hyperlink ref="D54" r:id="rId49"/>
+    <hyperlink ref="D55" r:id="rId50"/>
+    <hyperlink ref="D56" r:id="rId51"/>
+    <hyperlink ref="D57" r:id="rId52"/>
+    <hyperlink ref="D58" r:id="rId53"/>
+    <hyperlink ref="D59" r:id="rId54"/>
+    <hyperlink ref="D60" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="2"/>
